--- a/example/excel/测试表.xlsx
+++ b/example/excel/测试表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="map" sheetId="2" r:id="rId1"/>
@@ -345,7 +345,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,12 +355,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +692,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -722,16 +716,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -740,85 +734,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -837,7 +831,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1214,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1405,46 +1399,15 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="5">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3">
-        <v>5</v>
-      </c>
-      <c r="J7" s="3">
-        <v>6</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1456,36 +1419,30 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3">
         <v>2</v>
       </c>
       <c r="H8" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J8" s="3">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" s="3">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="5">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B9" s="7">
+        <v>2</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -1497,65 +1454,40 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="5">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>7</v>
-      </c>
-      <c r="G10" s="3">
-        <v>7</v>
-      </c>
-      <c r="H10" s="3">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3">
-        <v>11</v>
-      </c>
-      <c r="J10" s="3">
-        <v>12</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0.5</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="7"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -1567,41 +1499,111 @@
         <v>0</v>
       </c>
       <c r="F11" s="3">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3">
+        <v>9</v>
+      </c>
+      <c r="J11" s="3">
+        <v>10</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="5">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7</v>
+      </c>
+      <c r="H12" s="3">
         <v>8</v>
       </c>
-      <c r="G11" s="3">
+      <c r="I12" s="3">
+        <v>11</v>
+      </c>
+      <c r="J12" s="3">
+        <v>12</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="5">
         <v>7</v>
       </c>
-      <c r="H11" s="3">
+      <c r="B13" s="6">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7</v>
+      </c>
+      <c r="H13" s="3">
         <v>9</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I13" s="3">
         <v>13</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J13" s="3">
         <v>14</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M13" s="3">
         <v>0.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+    <row r="15" spans="1:15">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:B4">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:B14">
+  <conditionalFormatting sqref="A15:B16">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B7 A4:A11 A13:B14"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A8:B8 A4:A7 A9:A13 A15:B16"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/example/excel/测试表.xlsx
+++ b/example/excel/测试表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="map" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
   <si>
     <t>activity</t>
   </si>
@@ -114,13 +114,25 @@
     <t>ArrFloat[</t>
   </si>
   <si>
+    <t>items.reward{id</t>
+  </si>
+  <si>
+    <t>val}</t>
+  </si>
+  <si>
     <t>活动</t>
   </si>
   <si>
     <t>时间格式</t>
   </si>
   <si>
+    <t>使用内置子对象</t>
+  </si>
+  <si>
     <t>base</t>
+  </si>
+  <si>
+    <t>kv:baseObj:0,1,2,3</t>
   </si>
   <si>
     <t>这里会生成一个Obj的对象</t>
@@ -1208,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1220,10 +1232,12 @@
     <col min="10" max="11" width="9" style="3"/>
     <col min="12" max="12" width="33.375" style="3" customWidth="1"/>
     <col min="13" max="13" width="16.875" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="14" max="15" width="9" style="3"/>
+    <col min="16" max="16" width="24.5" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1232,7 +1246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1278,8 +1292,14 @@
       <c r="O2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1319,13 +1339,19 @@
       <c r="O3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:15">
+      <c r="P3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:17">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>5</v>
@@ -1336,8 +1362,11 @@
       <c r="M4" s="2">
         <v>1.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1360,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -1397,12 +1426,18 @@
       <c r="M6" s="3">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -1436,8 +1471,14 @@
       <c r="M8" s="3">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="5">
         <v>4</v>
       </c>
@@ -1477,12 +1518,18 @@
       <c r="M9" s="3">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="5"/>
       <c r="B10" s="7"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11" s="5">
         <v>5</v>
       </c>
@@ -1516,8 +1563,14 @@
       <c r="M11" s="3">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="5">
         <v>6</v>
       </c>
@@ -1551,8 +1604,14 @@
       <c r="M12" s="3">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="5">
         <v>7</v>
       </c>
@@ -1586,12 +1645,18 @@
       <c r="M13" s="3">
         <v>0.399999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P13" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
     </row>
@@ -1617,13 +1682,19 @@
   <sheetPr/>
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -1636,63 +1707,63 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/example/excel/测试表.xlsx
+++ b/example/excel/测试表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="map" sheetId="2" r:id="rId1"/>
@@ -90,7 +90,7 @@
     <t>]</t>
   </si>
   <si>
-    <t>Obj{id</t>
+    <t>Obj.drop{id</t>
   </si>
   <si>
     <t>num</t>
@@ -99,7 +99,7 @@
     <t>per}</t>
   </si>
   <si>
-    <t>ArrObj[{id</t>
+    <t>ArrObj.item[{id</t>
   </si>
   <si>
     <t>num}</t>
